--- a/artfynd/S 2729-2025 artfynd.xlsx
+++ b/artfynd/S 2729-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6653627</v>
+        <v>135171689</v>
       </c>
       <c r="B7" t="n">
-        <v>80477</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,37 +1266,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229504</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>HYLTE (06C0j02), Sm</t>
+          <t>Hylte, Hällabäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398073</v>
+        <v>398109</v>
       </c>
       <c r="R7" t="n">
-        <v>6349507</v>
+        <v>6349522</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,17 +1332,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1996-04-17</t>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1996-04-17</t>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>060209021 / PEL COLL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>Min 1 juv plus 2 other birds, probably juvenils following an adult</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,29 +1363,985 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Gammal ask</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135225794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>One juv at nest hole and one calling</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135226003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57280</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fare away c. 1km</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135236075</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135225873</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>No calls/song heard</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135228400</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>One young calling, and one adult 'singing'</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135226166</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57796</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135225840</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Madsen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6653627</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>HYLTE (06C0j02), Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>398073</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6349507</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1996-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1996-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>060209021 / PEL COLL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Gammal ask</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Gunnar Gummesson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>

--- a/artfynd/S 2729-2025 artfynd.xlsx
+++ b/artfynd/S 2729-2025 artfynd.xlsx
@@ -1367,12 +1367,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1613,12 +1613,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1867,12 +1867,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1985,12 +1985,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2108,12 +2108,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Madsen</t>
+          <t>Jesper Johannes  Madsen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/S 2729-2025 artfynd.xlsx
+++ b/artfynd/S 2729-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/914753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/681555</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2003434</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1892962</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225794</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1622,6 +1662,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135226003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1748,6 +1793,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1876,6 +1926,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225873</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1994,6 +2049,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135228400</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2117,6 +2177,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135226166</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2230,6 +2295,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225840</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2346,8 +2416,29 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6653627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2729-2025 artfynd.xlsx
+++ b/artfynd/S 2729-2025 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>135171689</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>135225794</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>135226003</v>
       </c>
       <c r="B9" t="n">
-        <v>57280</v>
+        <v>57285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135236075</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135225873</v>
       </c>
       <c r="B11" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>135228400</v>
       </c>
       <c r="B12" t="n">
-        <v>57824</v>
+        <v>57829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>135226166</v>
       </c>
       <c r="B13" t="n">
-        <v>57796</v>
+        <v>57801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>135225840</v>
       </c>
       <c r="B14" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2729-2025 artfynd.xlsx
+++ b/artfynd/S 2729-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6653627</v>
+        <v>135171689</v>
       </c>
       <c r="B7" t="n">
-        <v>80477</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,37 +1296,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229504</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>HYLTE (06C0j02), Sm</t>
+          <t>Hylte, Hällabäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398073</v>
+        <v>398109</v>
       </c>
       <c r="R7" t="n">
-        <v>6349507</v>
+        <v>6349522</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,17 +1362,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1996-04-17</t>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1996-04-17</t>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>060209021 / PEL COLL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>Min 1 juv plus 2 other birds, probably juvenils following an adult</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,34 +1393,1030 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Gammal ask</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171689</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135225794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>One juv at nest hole and one calling</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225794</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135226003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57285</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fare away c. 1km</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135226003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135236075</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236075</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135225873</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57781</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>No calls/song heard</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225873</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135228400</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57829</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>One young calling, and one adult 'singing'</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135228400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135226166</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57801</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135226166</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135225840</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hylte, Hällabäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>398102</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6349535</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Johannes  Madsen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135225840</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6653627</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>HYLTE (06C0j02), Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>398073</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6349507</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1996-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1996-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>060209021 / PEL COLL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Gammal ask</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Gunnar Gummesson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6653627</t>
         </is>
@@ -1412,6 +2430,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
